--- a/QCM4_1_PHY.xlsx
+++ b/QCM4_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831357BB-779A-41C7-BA4D-31224E48D407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16C4E9D-32EB-46D6-9359-AD682D520C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,14 +358,14 @@
   </si>
   <si>
     <t>On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement.
-&lt;img src="/images/PHY_QCM1_4_Q1.png" alt="A"class="h-20 block ml-auto my-1" /&gt;</t>
+&lt;img src="/images/PHY_QCM1_4_Q1.png" alt="A" class="h-20 block ml-auto my-1" /&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,12 +383,6 @@
       <sz val="10"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <b/>
@@ -498,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -508,9 +502,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -525,22 +516,22 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -892,531 +883,531 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="7"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14" t="s">
+      <c r="H3" s="13"/>
+      <c r="I3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="7"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="7"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="11" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12" t="s">
+      <c r="H6" s="11"/>
+      <c r="I6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="7"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="13" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14" t="s">
+      <c r="H8" s="13"/>
+      <c r="I8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12" t="s">
+      <c r="H10" s="11"/>
+      <c r="I10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14" t="s">
+      <c r="H11" s="13"/>
+      <c r="I11" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14" t="s">
+      <c r="H12" s="13"/>
+      <c r="I12" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12" t="s">
+      <c r="H13" s="11"/>
+      <c r="I13" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="7"/>
+      <c r="B14" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14" t="s">
+      <c r="H14" s="13"/>
+      <c r="I14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="11"/>
+      <c r="I15" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="13" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14" t="s">
+      <c r="H16" s="13"/>
+      <c r="I16" s="13" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="14" t="s">
+      <c r="C17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14" t="s">
+      <c r="H17" s="13"/>
+      <c r="I17" s="13" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12" t="s">
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="14" t="s">
+      <c r="C19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14" t="s">
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="12" t="s">
+      <c r="C20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="14" t="s">
+      <c r="H20" s="11"/>
+      <c r="I20" s="13" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="13" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="14" t="s">
+      <c r="C21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14" t="s">
+      <c r="H21" s="13"/>
+      <c r="I21" s="13" t="s">
         <v>82</v>
       </c>
     </row>

--- a/QCM4_1_PHY.xlsx
+++ b/QCM4_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16C4E9D-32EB-46D6-9359-AD682D520C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCD459C-CF63-43FB-A40E-521C50B20097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,8 +357,7 @@
     <t>$v \approx 12,2\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement.
-&lt;img src="/images/PHY_QCM1_4_Q1.png" alt="A" class="h-20 block ml-auto my-1" /&gt;</t>
+    <t>On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement. &lt;br&gt;&lt;br&gt; &lt;img src="/images/PHY_QCM1_4_Q1.png" alt="A" class="h-20 block mx-auto my-3" /&gt; &lt;br&gt;</t>
   </si>
 </sst>
 </file>

--- a/QCM4_1_PHY.xlsx
+++ b/QCM4_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCD459C-CF63-43FB-A40E-521C50B20097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1393D4E-F238-4412-8658-C274F3EA0FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
   <si>
     <t>Question</t>
   </si>
@@ -357,7 +357,10 @@
     <t>$v \approx 12,2\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement. &lt;br&gt;&lt;br&gt; &lt;img src="/images/PHY_QCM1_4_Q1.png" alt="A" class="h-20 block mx-auto my-3" /&gt; &lt;br&gt;</t>
+    <t xml:space="preserve">On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement. </t>
+  </si>
+  <si>
+    <t>PHY_QCM1_4_Q1.png</t>
   </si>
 </sst>
 </file>
@@ -907,7 +910,9 @@
       <c r="I2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">

--- a/QCM4_1_PHY.xlsx
+++ b/QCM4_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1393D4E-F238-4412-8658-C274F3EA0FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BDCF8F-BFEC-402F-BA48-1871069B62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="117">
   <si>
     <t>Question</t>
   </si>
@@ -123,9 +123,6 @@
     <t>La norme du vecteur vitesse est nulle.</t>
   </si>
   <si>
-    <t>Vitesse et accélération : Le centre d'inertie d'un solide de masse $m = 100\text{ g}$ est en mouvement. Il possède, à chaque instant, les coordonnées suivantes dans un repère orthonormé : $x(t) = 3.t$ et $y(t) = 4t^2 + 6t$.</t>
-  </si>
-  <si>
     <t>rectiligne</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>$400\text{ N}$</t>
   </si>
   <si>
-    <t>Equations horaires : Le vecteur position d'un mobile supposé ponctuel est défini par : $x = 20.t$</t>
-  </si>
-  <si>
     <t>une droite</t>
   </si>
   <si>
@@ -192,24 +186,12 @@
     <t>$V = 20\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t>$V = 36\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$V = 41\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
-    <t>$V = 49\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$a = 0$</t>
   </si>
   <si>
     <t>$a = 2\text{ m.s}^{-2}$</t>
   </si>
   <si>
-    <t>$a = 8\text{ m.s}^{-2}$</t>
-  </si>
-  <si>
     <t>$a = 20\text{ m.s}^{-2}$</t>
   </si>
   <si>
@@ -231,12 +213,6 @@
     <t>$x = 4t^2 + 5t ; y = 0$</t>
   </si>
   <si>
-    <t>Autre</t>
-  </si>
-  <si>
-    <t>Deuxième loi de Newton : Sur la piste d'un porte-avions, la poussée des moteurs d'un avion, de type « super étendard », est insuffisante pour le décollage. Il est donc nécessaire d'utiliser une catapulte qui exerce une force horizontale dirigée vers l'avant. L'avion atteint alors une vitesse de $50\text{ m.s}^{-1}$ en $2,5\text{ s}$. Le référentiel est le porte-avion navigant à vitesse constante sur une trajectoire rectiligne. Données : Poussée des moteurs d'un avion : $T = 50.10^3\text{ N}$. Masse d'un avion : $m = 6500\text{ kg}$. Longueur de la piste du porte-avion : $L = 50\text{ m}$. Intensité de pesanteur : $g = 10\text{ N.kg}^{-1}$.</t>
-  </si>
-  <si>
     <t>galiléen</t>
   </si>
   <si>
@@ -324,9 +300,6 @@
     <t>Le mobile n'est soumis que :</t>
   </si>
   <si>
-    <t>Une voiture roule à vitesse constante de $v\text{ m.s}^{-1}$ entre les points A et B puis accélère uniformément entre les points B et C, l'accélération a pour valeur $a = 4\text{ m.s}^{-2}$. A la date $t = 0$, le véhicule se trouve au point B qui est pris comme origine de l'axe soit $x_B = 0$. La trajectoire est rectiligne et est confondue avec l'axe des abscisses. Les équations horaires du mouvement de la voiture, pour $t &gt; 0$, s'écrivent :</t>
-  </si>
-  <si>
     <t>Le référentiel utilisé est un référentiel :</t>
   </si>
   <si>
@@ -357,10 +330,62 @@
     <t>$v \approx 12,2\text{ m.s}^{-1}$</t>
   </si>
   <si>
-    <t xml:space="preserve">On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement. </t>
-  </si>
-  <si>
     <t>PHY_QCM1_4_Q1.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On présente ci-dessous les trajectoires, le vecteur-vitesse, le vecteur-accélération du centre d'inertie G d'une balle ou le vecteur représentant la résultante des forces exercées sur la balle en mouvement. </t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Vitesse et accélération : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Le centre d'inertie d'un solide de masse $m = 100\text{ g}$ est en mouvement. Il possède, à chaque instant, les coordonnées suivantes dans un repère orthonormé : $x(t) = 3.t$ et $y(t) = 4t^2 + 6t$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Equations horaires : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Le vecteur position d'un mobile supposé ponctuel est défini par : $x = 20.t$ et $y = 2t^2 + 20t + 2$.</t>
+  </si>
+  <si>
+    <t>$V \approx 20\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$V \approx 36\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$V \approx 41\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$V \approx 49\text{ m.s}^{-1}$</t>
+  </si>
+  <si>
+    <t>$a = 10\text{ m.s}^{-2}$</t>
+  </si>
+  <si>
+    <t>Une voiture roule à vitesse constante de $5\text{ m.s}^{-1}$ entre les points A et B puis accélère uniformément entre les points B et C, l'accélération a pour valeur $a = 4\text{ m.s}^{-2}$. A la date $t = 0$, le véhicule se trouve au point B qui est pris comme origine de l'axe soit $x_B = 0$. La trajectoire est rectiligne et est confondue avec l'axe des abscisses. 
+Les équations horaires du mouvement de la voiture, supposée ponctuelle, entre les points B et C vaut :</t>
+  </si>
+  <si>
+    <t>$x = 2t^2 + 5t + 1 ; y = 0$</t>
+  </si>
+  <si>
+    <t>$x =0 ; y = 2t^2 + 5t$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Deuxième loi de Newton : &lt;/b&gt;&lt;/center&gt;
+&lt;br&gt;Sur la piste d'un porte-avions, la poussée des moteurs d'un avion, de type « super étendard », est insuffisante pour le décollage. Il est donc nécessaire d'utiliser une catapulte qui exerce une force horizontale dirigée vers l'avant. L'avion atteint alors une vitesse de $50\text{ m.s}^{-1}$ en $2,5\text{ s}$. 
+Le référentiel est le porte-avion navigant à vitesse constante sur une trajectoire rectiligne. 
+&lt;br&gt;Données : 
+Poussée des moteurs d'un avion : $T = 50.10^3\text{ N}$. 
+Masse d'un avion : $m = 6500\text{ kg}$. 
+Longueur de la piste du porte-avion : $L = 50\text{ m}$. 
+Intensité de pesanteur : $g = 10\text{ N.kg}^{-1}$.</t>
+  </si>
+  <si>
+    <t>$a = 50\text{ m.s}^{-2}$</t>
+  </si>
+  <si>
+    <t>$R = 6,5.10^4\text{ N}$</t>
+  </si>
+  <si>
+    <t>$R = 6,5.10^5\text{ N}$</t>
   </si>
 </sst>
 </file>
@@ -886,10 +911,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -911,14 +936,14 @@
         <v>15</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
@@ -945,7 +970,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="10" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -972,7 +997,7 @@
     <row r="5" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
@@ -999,7 +1024,7 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="10" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
@@ -1023,31 +1048,31 @@
       <c r="J6" s="5"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>36</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -1055,26 +1080,26 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="F8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="G8" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -1082,28 +1107,28 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="12" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -1111,26 +1136,26 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -1138,55 +1163,55 @@
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="F11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="G11" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="F12" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="G12" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -1194,26 +1219,26 @@
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -1221,198 +1246,204 @@
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="12" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="13" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="13" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" s="11"/>
+        <v>114</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="12" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+        <v>116</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="H19" s="13"/>
       <c r="I19" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="10" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="12" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/QCM4_1_PHY.xlsx
+++ b/QCM4_1_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BDCF8F-BFEC-402F-BA48-1871069B62F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE88C958-F72A-4B4E-B017-345EDF4F9E66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
   <si>
     <t>Question</t>
   </si>
@@ -183,9 +183,6 @@
     <t>autre</t>
   </si>
   <si>
-    <t>$V = 20\text{ m.s}^{-1}$</t>
-  </si>
-  <si>
     <t>$a = 0$</t>
   </si>
   <si>
@@ -204,9 +201,6 @@
     <t>à sa masse</t>
   </si>
   <si>
-    <t>$x = 2t^2 + vt ; y = 0$</t>
-  </si>
-  <si>
     <t>$x = 5t ; y = 2t^2 + 5t$</t>
   </si>
   <si>
@@ -256,9 +250,6 @@
   </si>
   <si>
     <t>$8,0.10^6\text{ J}$</t>
-  </si>
-  <si>
-    <t>À déterminer</t>
   </si>
   <si>
     <t>Le mouvement de la représentation n°1 est :</t>
@@ -361,9 +352,6 @@
   <si>
     <t>Une voiture roule à vitesse constante de $5\text{ m.s}^{-1}$ entre les points A et B puis accélère uniformément entre les points B et C, l'accélération a pour valeur $a = 4\text{ m.s}^{-2}$. A la date $t = 0$, le véhicule se trouve au point B qui est pris comme origine de l'axe soit $x_B = 0$. La trajectoire est rectiligne et est confondue avec l'axe des abscisses. 
 Les équations horaires du mouvement de la voiture, supposée ponctuelle, entre les points B et C vaut :</t>
-  </si>
-  <si>
-    <t>$x = 2t^2 + 5t + 1 ; y = 0$</t>
   </si>
   <si>
     <t>$x =0 ; y = 2t^2 + 5t$</t>
@@ -386,6 +374,9 @@
   </si>
   <si>
     <t>$R = 6,5.10^5\text{ N}$</t>
+  </si>
+  <si>
+    <t>$x = 2t^2 + 5t ; y = 0$</t>
   </si>
 </sst>
 </file>
@@ -911,10 +902,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>3</v>
@@ -933,17 +924,17 @@
       </c>
       <c r="H2" s="11"/>
       <c r="I2" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
@@ -970,7 +961,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>3</v>
@@ -989,7 +980,7 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="6"/>
@@ -997,7 +988,7 @@
     <row r="5" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>3</v>
@@ -1024,7 +1015,7 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>3</v>
@@ -1050,10 +1041,10 @@
     </row>
     <row r="7" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>3</v>
@@ -1080,7 +1071,7 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>3</v>
@@ -1104,31 +1095,29 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>77</v>
+      <c r="H9" s="14"/>
+      <c r="I9" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -1136,7 +1125,7 @@
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>3</v>
@@ -1163,7 +1152,7 @@
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>3</v>
@@ -1189,10 +1178,10 @@
     </row>
     <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
@@ -1211,7 +1200,7 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -1219,26 +1208,26 @@
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="H13" s="11"/>
       <c r="I13" s="11" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -1246,22 +1235,22 @@
     <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="F14" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13" t="s">
@@ -1272,19 +1261,19 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="F15" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>51</v>
@@ -1297,153 +1286,153 @@
     <row r="16" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="13" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="G17" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>55</v>
-      </c>
       <c r="F18" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="G20" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="H20" s="11"/>
-      <c r="I20" s="13" t="s">
-        <v>67</v>
+      <c r="I20" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="12" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="G21" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
